--- a/structuring/250922 Analyse der Requirements.xlsx
+++ b/structuring/250922 Analyse der Requirements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telefonicacorp-my.sharepoint.com/personal/thorsten_heinze_telefonica_com/Documents/Documents/Aktuell/Projekte/140502 SDN/71 UseCases/PerformanceManagement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heinztho\Documents\vscode\ud\_PerformanceManagement\structuring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{F540496B-957B-498A-8CDA-EB0A6407C1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B733355-AAD6-4B49-82CC-4CD5070D4C10}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42D7EB1-8E7B-4106-8646-9CFDC2AA9216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="840" windowWidth="24930" windowHeight="22845" xr2:uid="{8977F850-12B3-4A4D-A510-C2D2F506B805}"/>
+    <workbookView xWindow="11940" yWindow="2235" windowWidth="24930" windowHeight="22845" xr2:uid="{8977F850-12B3-4A4D-A510-C2D2F506B805}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>APT, NetExplorer, Mycom</t>
   </si>
@@ -47,38 +47,7 @@
     <t>On-demand upload of latest PM data of individual traffic interfaces shall be supported</t>
   </si>
   <si>
-    <t>The PM data shall be collected from all connected devices and be forwarded to the Consumers</t>
-  </si>
-  <si>
-    <t>…all connected devices…:
-- Der ManagementPlaneManager liefert die Aussage welche Devices connected sind
-- Diese Liste der connected devices ist auch Grundlage der Eigenperformancemessung
-… forwarded to the Consumers … :
-- Die MW Domäne wird den Konsumenten die PM Daten über Kafkabus zu Verfügung stellen</t>
-  </si>
-  <si>
-    <t>In case of incompleteness, it shall be autonomously attempted to complete the data</t>
-  </si>
-  <si>
-    <t>The PM data shall be provided with a maximum delay (age of the oldest value set) of 6 hours
-(an improvement to a maximum delay of 3 hours shall be attempted)</t>
-  </si>
-  <si>
-    <t>- Die Periodenlänge von 6Stunden scheint durch die gegenwärtig Installation erreicht
-- Für 3Stunden wird der ControllerDomainManager benötigt um mehrere OpenDaylight Instanzen im Loadsharing betreiben zu können. (Es besteht ferner das Risiko, dass der MWDI zur Schwachstelle werden könnte)</t>
-  </si>
-  <si>
-    <t>Gegenwärtig werden PM Daten geräteweise geliefert interfaceweise Lieferung ist zu ergänzen:
-- DPD soll 3 Services bereitstellen:
-  - für individuelle AirInterfaces
-  - für individuelle EthernetContainer auf AirInterfaces
-  - für das gesamte Gerät (zur Abdeckung der EthernetContainer, die nicht auf AirI. liegen)</t>
-  </si>
-  <si>
     <t>Plausibility</t>
-  </si>
-  <si>
-    <t>Uploaded PM data shall be checked for plausibility</t>
   </si>
   <si>
     <t>Implausible data shall be replaced or deleted according to generic rules</t>
@@ -93,11 +62,6 @@
     <t>- Ergänzungen (durch Wechsel auf ONF) sind noch fachlich abzustimmen
 - Plausibilitätsanpassung in Mycom sind bekannt und in Issue #14 dokumentiert
 - Plausibilitätsanpassung in Comarch sind noch unbekannt</t>
-  </si>
-  <si>
-    <t>- Das Auffüllen von fehlenden 15Minutenmessungen wird nicht betrieben.
-- Die autonome Vervollständigung bezieht sich also nur auf das Wiederholen des regelmäßigen Uploads im Falle von Nichterreichbarkeit.
-- Die Vervollständigung soll über Adressieren der Live Pfade am MWDI geschehen</t>
   </si>
   <si>
     <t>Semantic</t>
@@ -162,15 +126,6 @@
   </si>
   <si>
     <t>Calculation of derived KPIs shall be supported (as far as they get used by the majority of Consumers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- DPD shall
-  - shall receive AVC notifications about the date-of-latest-change attribute from MWDI
-  - upload the PM data from MWDI
-  - process it (incl. Plausibilitätsanpassung
-  - pass it to Kafka
-  - store the data for a period of 48hours
-</t>
   </si>
   <si>
     <t xml:space="preserve">- DPD soll die Berechnung abgeleiteter KPIs durchführen
@@ -190,19 +145,10 @@
     <t>Complement with configuration data as far as it can be harmonized across the Consumers</t>
   </si>
   <si>
-    <t>- Grundgerüst ist eine Kopie des APTP reduziert auf die PM Funktionalität
-- Bedarfe des NetExplorers müssen in den Bestand konsolidiert werden
-- Werden Configdaten mit Perfdaten verknüpft, so soll dies im DPD geschehen
-- Gegenwärtig werden die Configdaten jeweils zum Zeitpunkt der Weitergabe der PM Daten aktuell im MWDI angefragt, und übergeben (angesichts der seltenen Änderung an ConfigDaten und der Unschärfe die durch die Periodenlänge entsteht, ist diese Form der Weitergabe nicht ideal; Anwendung von Änderungsmittelungen prüfen)</t>
-  </si>
-  <si>
     <t>Service Quality Monitoring</t>
   </si>
   <si>
     <t>Statistics about the completeness and quality of the PM data shall be provided</t>
-  </si>
-  <si>
-    <t>- Die Qualität der eigenen Lieferung soll ständig überwacht und dokumentiert werden</t>
   </si>
   <si>
     <t>Requirement</t>
@@ -257,15 +203,94 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Nutzen der SlidingWindowFunktion des MWDI
+    <t>Regular uploading:
+- In case of incompleteness, it shall be autonomously attempted to complete the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- KafkaMessageBus
+- KafkaStreams 
+- DPMDP: KafkaProvider
+</t>
+  </si>
+  <si>
+    <t>- MWDI ES nach DPMDP ES Replikation
+- MWDI: Transmitter of attribute value changed notifications (mindestens für date-of-latest-change Attribut)
+- DPMDP: Notification receiver</t>
+  </si>
+  <si>
+    <t>- potentiell kein Deliverable</t>
+  </si>
+  <si>
+    <t>Regular uploading:
+- The PM data shall be provided with a maximum delay (age of the oldest value set) of 6 hours
+(an improvement to a maximum delay of 3 hours shall be attempted)</t>
+  </si>
+  <si>
+    <t>- MWDI: Adaption SlidingWindowModul</t>
+  </si>
+  <si>
+    <t>Out of scope:
+- Das Auffüllen von fehlenden 15Minutenmessungen wird nicht betrieben.
+Noch zu klären:
+- wird eine Wiederholung bei erfolglosem Upload noch gebracht, wenn eh alle 3h ein Upload erfolgt?
+- Falls ja, wird die Vervollständigung über Adressieren der Live Pfade am MWDI geschehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gegenwärtig werden PM Daten geräteweise geliefert interfaceweise Lieferung ist zu ergänzen:
+- DPMDP soll 3 Services bereitstellen:
+  - für individuelle AirInterfaces
+  - für individuelle EthernetContainer auf AirInterfaces
+  - für das gesamte Gerät (zur Abdeckung der EthernetContainer, die nicht auf AirI. liegen)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- DPMDP: Funktion, die {NeId, LinkId} nach {MountName, Uuid, LocalId} übersetzt (auf Wiederverwendbarkeit in anderen Applications achten)
+- DPMDP: Funktion, die {NeId, EthernetPortIdentifier} nach {MountName, Uuid, LocalId} übersetzt (auf Wiederverwendbarkeit in anderen Applications achten)
+- adressieren des LivePaths am MWDI
+- DPMDP: Funktionen zur Prozessierung der regelmäßigen Uploads (ganzes CC) so schneiden, dass auch ein individuellen Interface damit prozessiert werden kann (doppelte Implementierung von z.B. Löschung der DefaultValues sollte unbedingt vermieden werden)
+- DPMDP: on-demand-services als REST Requests (assynchron nur falls notwendig) ausführen
+- DPMDP: Dass der Request gegen die LiveDomäne eine Aktualisierung des date-of-latest-change Attributs verursacht (incl. AVC-Notification) und damit auch die zyklische Prozessierung der Daten auslöst, soll dabei tolleriert werden.
+</t>
+  </si>
+  <si>
+    <t>Nutzen der SlidingWindowFunktion des MWDI
 Arbeitsannahme zur Weitergabe der Daten von MWDI nach DPMDP:
 - DPMDP bekommt ElasticSearch Replik von MWDI
+…all connected devices…:
+- Der ManagementPlaneManager liefert die Aussage welche Devices connected sind
+- Diese Liste der connected devices ist auch Grundlage der Eigenperformancemessung
 Noch zu klären:
 - Wie wird DPMDP auf der Applikationsebene über neue Daten informiert?
-</t>
-  </si>
-  <si>
-    <t>… hier geht's weiter …</t>
+   (im Falle von Notifications auf Applikationsebene (z.B. AVC notifications about the date-of-latest-change attribute) ist über ein Verzögerungsglied nachzudenken, damit sichergestellt ist, dass die neuen Daten bereits in der Datenbank des DPMDP angekommen sind.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Die Qualität der eigenen Lieferung soll ständig überwacht und dokumentiert werden
+- Zur Unterstützung der Entstörung sollen die berechneten Daten für 48h gespeichert werden
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Grundgerüst ist eine Kopie des APTP reduziert auf die PM Funktionalität
+- Bedarfe des NetExplorers müssen in den Bestand konsolidiert werden
+- Werden Configdaten mit Perfdaten verknüpft, so soll dies im DPD geschehen
+- Gegenwärtig werden die Configdaten jeweils zum Zeitpunkt der Weitergabe der PM Daten aktuell im MWDI angefragt, und übergeben (angesichts der seltenen Änderung an ConfigDaten und der Unschärfe die durch die Periodenlänge entsteht, ist diese Form der Weitergabe nicht ideal; Anwendung von Änderungsmittelungen prüfen)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uploaded PM data shall be checked for plausibility
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Tx-Level mit Capability daten vergleichen
+- Rx-Level mit Bereichsvorgabe vergleichen
+- Temperatur mit Bereichsvorgabe vergleichen
+- Modulationen mit 0s or -1s löschen
+- _alle Änderungen an den Daten sind mit den Fachexperten abzustimmen_
+</t>
+  </si>
+  <si>
+    <t>- DPMDP: Funktion zum Löschen unnötiger Datensätz
+'- DPMDP: Funktion zum 
+     hier geht's weiter</t>
   </si>
 </sst>
 </file>
@@ -317,28 +342,28 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -675,270 +700,269 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BDB2A76-4123-4374-A8E8-DC03FE0585DA}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="1"/>
-    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="88.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="57" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="2" width="11.42578125" style="3"/>
+    <col min="3" max="3" width="49.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="88.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="57" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="C4" s="2" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="C5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2" t="s">
+      <c r="E11" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="C13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="C15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="C19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="C24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="195" x14ac:dyDescent="0.25">
+      <c r="C26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="C28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="D9" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="C20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="C25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="180" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="195" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="C31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
